--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126348499</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126348501</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126348503</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126348505</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126348502</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>126348497</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>126348498</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>126348500</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126348499</v>
+        <v>91992991</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412630</v>
+        <v>412616</v>
       </c>
       <c r="R2" t="n">
-        <v>6965613</v>
+        <v>6966018</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126348501</v>
+        <v>126348497</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412693</v>
+        <v>412701</v>
       </c>
       <c r="R3" t="n">
-        <v>6965664</v>
+        <v>6965749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348503</v>
+        <v>126348498</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412816</v>
+        <v>412636</v>
       </c>
       <c r="R4" t="n">
-        <v>6965745</v>
+        <v>6965623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +953,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348505</v>
+        <v>126348499</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412820</v>
+        <v>412630</v>
       </c>
       <c r="R5" t="n">
-        <v>6965733</v>
+        <v>6965613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348502</v>
+        <v>126348500</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412740</v>
+        <v>412646</v>
       </c>
       <c r="R6" t="n">
-        <v>6965691</v>
+        <v>6965606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1157,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348497</v>
+        <v>126348501</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412701</v>
+        <v>412693</v>
       </c>
       <c r="R7" t="n">
-        <v>6965749</v>
+        <v>6965664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348498</v>
+        <v>126348502</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412636</v>
+        <v>412740</v>
       </c>
       <c r="R8" t="n">
-        <v>6965623</v>
+        <v>6965691</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348500</v>
+        <v>126348503</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412646</v>
+        <v>412816</v>
       </c>
       <c r="R9" t="n">
-        <v>6965606</v>
+        <v>6965745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,6 +1487,108 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126348505</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412820</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6965733</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91992991</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348498</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348500</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348501</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,8 +1634,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>